--- a/data/dokumentasi/dokumentasi_penomoran.xlsx
+++ b/data/dokumentasi/dokumentasi_penomoran.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4592,6 +4592,2610 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>SPK/KP/00152/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>2</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>SPK/KP/00153/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>2</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>SPK/KP/00154/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Minggu</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>5</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>SPK/KP/00155/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>6</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>SPK/KP/00156/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>6</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>SPK/KP/00157/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>7</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>SPK/KP/00158/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>7</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>SPK/KP/00159/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>8</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>SPK/KP/00160/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>8</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>SPK/KP/00161/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>9</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>SPK/KP/00162/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>9</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>SPK/KP/00163/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>13</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>SPK/KP/00164/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>14</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>SPK/KP/00165/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>15</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>SPK/KP/00166/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>16</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>SPK/KP/00167/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>20</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>SPK/KP/00168/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>20</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>SPK/KP/00169/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>21</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>SPK/KP/00170/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>22</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>SPK/KP/00171/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>22</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>SPK/KP/00172/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>23</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>SPK/KP/00173/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>23</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>SPK/KP/00174/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>27</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>SPK/KP/00175/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>29</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>SPK/KP/00176/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>30</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>SPK/KP/00177/07/2026/81</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>3</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>SPK/KP/00178/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>3</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>SPK/KP/00179/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>4</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>SPK/KP/00180/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>4</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>SPK/KP/00181/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>5</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>SPK/KP/00182/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>5</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>SPK/KP/00183/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>6</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>SPK/KP/00184/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>6</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>SPK/KP/00185/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>10</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>SPK/KP/00186/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>11</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>SPK/KP/00187/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>12</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>SPK/KP/00188/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>12</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>SPK/KP/00189/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>13</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>SPK/KP/00190/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>13</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>SPK/KP/00191/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>18</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>SPK/KP/00192/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>19</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>SPK/KP/00193/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>20</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>SPK/KP/00194/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>24</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>SPK/KP/00195/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>24</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>SPK/KP/00196/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>26</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>SPK/KP/00197/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>26</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>SPK/KP/00198/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>31</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Agustus</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>SPK/KP/00199/08/2026/81</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>25</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>SPK/KP/00231/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>SPK/KP/00200/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>SPK/KP/00237/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Standarisasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>1</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>SPK/KP/00201/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>2</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>SPK/KP/00202/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>3</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>SPK/KP/00203/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>3</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>SPK/KP/00238/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Standarisasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>3</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>SPK/KP/00204/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>7</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>SPK/KP/00205/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>7</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>SPK/KP/00239/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Standarisasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>7</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>SPK/KP/00206/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>8</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>SPK/KP/00207/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>9</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>SPK/KP/00208/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>9</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>SPK/KP/00209/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Standarisasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>9</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>SPK/KP/00210/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>10</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>SPK/KP/00211/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>10</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>SPK/KP/00212/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Standarisasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>10</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>SPK/KP/00213/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>14</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>SPK/KP/00214/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>14</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>SPK/KP/00215/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Standarisasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>14</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>SPK/KP/00216/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>15</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>SPK/KP/00217/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>15</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>SPK/KP/00218/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Standarisasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>15</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>SPK/KP/00219/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>16</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>SPK/KP/00220/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>16</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>SPK/KP/00221/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Standarisasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>16</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>SPK/KP/00222/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>17</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>SPK/KP/00223/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>17</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>SPK/KP/00224/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Standarisasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>17</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>SPK/KP/00225/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>21</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>SPK/KP/00226/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>22</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>SPK/KP/00227/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Standarisasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>22</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>SPK/KP/00228/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>24</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>SPK/KP/00229/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>24</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>SPK/KP/00240/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Standarisasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>24</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>SPK/KP/00230/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>25</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>SPK/KP/00241/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Standarisasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>28</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>SPK/KP/00232/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>28</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>SPK/KP/00242/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Standarisasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>28</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>SPK/KP/00233/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>29</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>SPK/KP/00234/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>29</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>SPK/KP/00235/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>30</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>SPK/KP/00236/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Penbangkom</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>29</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>SPK/KP/00243/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Pelayanan dan Fasilitasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>30</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>SPK/KP/00244/09/2026/81</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Surat Perintah Kerja Lembur Bidang Pelayanan dan Fasilitasi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
